--- a/Result/profitability/6278.xlsx
+++ b/Result/profitability/6278.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.71</v>
       </c>
       <c r="M2" t="n">
-        <v>2.24375</v>
+        <v>2.30625</v>
       </c>
       <c r="N2" t="n">
-        <v>12.65625</v>
+        <v>12.51375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.56</v>
       </c>
       <c r="M3" t="n">
-        <v>2.155</v>
+        <v>2.2</v>
       </c>
       <c r="N3" t="n">
-        <v>12.62125</v>
+        <v>12.26625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.34</v>
       </c>
       <c r="M4" t="n">
-        <v>2.02125</v>
+        <v>2.0075</v>
       </c>
       <c r="N4" t="n">
-        <v>12.2125</v>
+        <v>12.01625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.22</v>
       </c>
       <c r="M5" t="n">
-        <v>1.68875</v>
+        <v>1.83</v>
       </c>
       <c r="N5" t="n">
-        <v>11.24625</v>
+        <v>11.2025</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.64</v>
       </c>
       <c r="M6" t="n">
-        <v>1.56375</v>
+        <v>1.6125</v>
       </c>
       <c r="N6" t="n">
-        <v>10.6975</v>
+        <v>10.5875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>2.26</v>
       </c>
       <c r="M7" t="n">
-        <v>1.54875</v>
+        <v>1.58375</v>
       </c>
       <c r="N7" t="n">
-        <v>10.2775</v>
+        <v>10.11875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>2.12</v>
       </c>
       <c r="M8" t="n">
-        <v>1.5025</v>
+        <v>1.5775</v>
       </c>
       <c r="N8" t="n">
-        <v>9.88125</v>
+        <v>9.94125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>1.4775</v>
       </c>
       <c r="N9" t="n">
-        <v>9.66625</v>
+        <v>9.666250000000002</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6278</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>13231</v>
+      </c>
+      <c r="D75" t="n">
+        <v>11670</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="G75" t="n">
+        <v>818</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.18%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>87</v>
+      </c>
+      <c r="J75" t="n">
+        <v>905</v>
+      </c>
+      <c r="K75" t="n">
+        <v>800</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.37625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.73625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2764976958525347</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.4799999999999986</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.04244031830238715</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.6890243902439026</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.3500000000000014</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02883031301482708</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
